--- a/data/status_report.xlsx
+++ b/data/status_report.xlsx
@@ -34,13 +34,13 @@
       <color rgb="00000000"/>
     </font>
     <font>
+      <color rgb="00006100"/>
+    </font>
+    <font>
       <color rgb="009C0006"/>
     </font>
-    <font>
-      <color rgb="00006100"/>
-    </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -54,12 +54,17 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="00FFEB9C"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="00FFC7CE"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFEB9C"/>
+        <fgColor rgb="00C6EFCE"/>
       </patternFill>
     </fill>
     <fill>
@@ -80,23 +85,24 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -621,87 +627,79 @@
         <v>1</v>
       </c>
       <c r="E2" t="n">
-        <v>-178.59</v>
+        <v>-169.315</v>
       </c>
       <c r="F2" t="n">
-        <v>88.95</v>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L2" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M2" s="3" t="inlineStr">
-        <is>
-          <t>❌</t>
-        </is>
-      </c>
-      <c r="N2" s="3" t="inlineStr">
-        <is>
-          <t>❌</t>
-        </is>
-      </c>
-      <c r="O2" s="3" t="inlineStr">
-        <is>
-          <t>❌</t>
-        </is>
-      </c>
-      <c r="P2" s="3" t="inlineStr">
-        <is>
-          <t>❌</t>
-        </is>
-      </c>
-      <c r="Q2" s="3" t="inlineStr">
-        <is>
-          <t>❌</t>
-        </is>
-      </c>
-      <c r="R2" s="3" t="inlineStr">
-        <is>
-          <t>❌</t>
-        </is>
-      </c>
-      <c r="S2" s="3" t="inlineStr">
-        <is>
-          <t>❌</t>
-        </is>
-      </c>
-      <c r="T2" s="3" t="inlineStr">
+        <v>87.384</v>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>TRACKED — analysis pending</t>
+        </is>
+      </c>
+      <c r="H2" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="K2" t="n">
+        <v>2647</v>
+      </c>
+      <c r="L2" s="3" t="inlineStr">
+        <is>
+          <t>15 runs (top 5 by duration): f2283–f2284 (38.1s–38.1s, 0.0s) | f651 (10.9s, isolated) | f1050 (17.5s, isolated) | f1123 (18.7s, isolated) | f1421 (23.7s, isolated) ... and 10 more</t>
+        </is>
+      </c>
+      <c r="M2" s="4" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="N2" s="4" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="O2" s="5" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="P2" s="5" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="Q2" s="5" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="R2" s="5" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="S2" s="5" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="T2" s="5" t="inlineStr">
         <is>
           <t>❌</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>global</t>
-        </is>
-      </c>
-      <c r="V2" s="2" t="inlineStr"/>
+          <t>per-video</t>
+        </is>
+      </c>
+      <c r="V2" s="3" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -728,12 +726,12 @@
       <c r="F3" t="n">
         <v>1.054</v>
       </c>
-      <c r="G3" s="4" t="inlineStr">
+      <c r="G3" s="6" t="inlineStr">
         <is>
           <t>NEEDS WORK — high dropout (26.1%)</t>
         </is>
       </c>
-      <c r="H3" s="4" t="n">
+      <c r="H3" s="6" t="n">
         <v>26.09</v>
       </c>
       <c r="I3" t="n">
@@ -745,47 +743,47 @@
       <c r="K3" t="n">
         <v>115</v>
       </c>
-      <c r="L3" s="2" t="inlineStr">
+      <c r="L3" s="3" t="inlineStr">
         <is>
           <t>7 runs: f104–f106 (1.7s–1.8s, 0.0s) | f138–f141 (2.3s–2.4s, 0.1s) | f144–f145 (2.4s–2.4s, 0.0s) | f147 (2.5s, isolated) | f149–f151 (2.5s–2.5s, 0.0s) | f153–f167 (2.6s–2.8s, 0.2s) | f201–f202 (3.4s–3.4s, 0.0s)</t>
         </is>
       </c>
-      <c r="M3" s="5" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="N3" s="3" t="inlineStr">
-        <is>
-          <t>❌</t>
-        </is>
-      </c>
-      <c r="O3" s="5" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="P3" s="3" t="inlineStr">
-        <is>
-          <t>❌</t>
-        </is>
-      </c>
-      <c r="Q3" s="3" t="inlineStr">
-        <is>
-          <t>❌</t>
-        </is>
-      </c>
-      <c r="R3" s="3" t="inlineStr">
-        <is>
-          <t>❌</t>
-        </is>
-      </c>
-      <c r="S3" s="3" t="inlineStr">
-        <is>
-          <t>❌</t>
-        </is>
-      </c>
-      <c r="T3" s="3" t="inlineStr">
+      <c r="M3" s="4" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="N3" s="5" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="O3" s="4" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="P3" s="5" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="Q3" s="5" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="R3" s="5" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="S3" s="5" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="T3" s="5" t="inlineStr">
         <is>
           <t>❌</t>
         </is>
@@ -795,7 +793,7 @@
           <t>global</t>
         </is>
       </c>
-      <c r="V3" s="2" t="inlineStr">
+      <c r="V3" s="3" t="inlineStr">
         <is>
           <t>⚠ dropout &gt; 10%
 ⚠ no per-video HSV calibration</t>
@@ -822,77 +820,69 @@
         <v>1</v>
       </c>
       <c r="E4" t="n">
-        <v>0.72</v>
+        <v>0.707</v>
       </c>
       <c r="F4" t="n">
-        <v>92.84</v>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M4" s="3" t="inlineStr">
-        <is>
-          <t>❌</t>
-        </is>
-      </c>
-      <c r="N4" s="3" t="inlineStr">
-        <is>
-          <t>❌</t>
-        </is>
-      </c>
-      <c r="O4" s="3" t="inlineStr">
-        <is>
-          <t>❌</t>
-        </is>
-      </c>
-      <c r="P4" s="3" t="inlineStr">
-        <is>
-          <t>❌</t>
-        </is>
-      </c>
-      <c r="Q4" s="3" t="inlineStr">
-        <is>
-          <t>❌</t>
-        </is>
-      </c>
-      <c r="R4" s="3" t="inlineStr">
-        <is>
-          <t>❌</t>
-        </is>
-      </c>
-      <c r="S4" s="3" t="inlineStr">
-        <is>
-          <t>❌</t>
-        </is>
-      </c>
-      <c r="T4" s="3" t="inlineStr">
+        <v>84.806</v>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>TRACKED — analysis pending</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="n">
+        <v>7.12</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="J4" t="n">
+        <v>7.12</v>
+      </c>
+      <c r="K4" t="n">
+        <v>983</v>
+      </c>
+      <c r="L4" s="3" t="inlineStr">
+        <is>
+          <t>8 runs: f181 (3.0s, isolated) | f210–f212 (3.5s–3.5s, 0.0s) | f219 (3.7s, isolated) | f221 (3.7s, isolated) | f252–f312 (4.2s–5.2s, 1.0s) | f345 (5.8s, isolated) | f360 (6.0s, isolated) | f362 (6.0s, isolated)</t>
+        </is>
+      </c>
+      <c r="M4" s="4" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="N4" s="4" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="O4" s="5" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="P4" s="5" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="Q4" s="5" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="R4" s="5" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="S4" s="5" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="T4" s="5" t="inlineStr">
         <is>
           <t>❌</t>
         </is>
@@ -902,7 +892,11 @@
           <t>global</t>
         </is>
       </c>
-      <c r="V4" s="2" t="inlineStr"/>
+      <c r="V4" s="3" t="inlineStr">
+        <is>
+          <t>⚠ no per-video HSV calibration</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -924,77 +918,69 @@
         <v>1</v>
       </c>
       <c r="E5" t="n">
-        <v>36.58</v>
+        <v>35.538</v>
       </c>
       <c r="F5" t="n">
-        <v>94.34</v>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M5" s="3" t="inlineStr">
-        <is>
-          <t>❌</t>
-        </is>
-      </c>
-      <c r="N5" s="3" t="inlineStr">
-        <is>
-          <t>❌</t>
-        </is>
-      </c>
-      <c r="O5" s="3" t="inlineStr">
-        <is>
-          <t>❌</t>
-        </is>
-      </c>
-      <c r="P5" s="3" t="inlineStr">
-        <is>
-          <t>❌</t>
-        </is>
-      </c>
-      <c r="Q5" s="3" t="inlineStr">
-        <is>
-          <t>❌</t>
-        </is>
-      </c>
-      <c r="R5" s="3" t="inlineStr">
-        <is>
-          <t>❌</t>
-        </is>
-      </c>
-      <c r="S5" s="3" t="inlineStr">
-        <is>
-          <t>❌</t>
-        </is>
-      </c>
-      <c r="T5" s="3" t="inlineStr">
+        <v>90.58199999999999</v>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>TRACKED — analysis pending</t>
+        </is>
+      </c>
+      <c r="H5" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="J5" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="K5" t="n">
+        <v>1059</v>
+      </c>
+      <c r="L5" s="3" t="inlineStr">
+        <is>
+          <t>3 runs: f97–f98 (1.6s–1.6s, 0.0s) | f171–f181 (2.9s–3.0s, 0.2s) | f213–f215 (3.6s–3.6s, 0.0s)</t>
+        </is>
+      </c>
+      <c r="M5" s="4" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="N5" s="4" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="O5" s="5" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="P5" s="5" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="Q5" s="5" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="R5" s="5" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="S5" s="5" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="T5" s="5" t="inlineStr">
         <is>
           <t>❌</t>
         </is>
@@ -1004,7 +990,11 @@
           <t>global</t>
         </is>
       </c>
-      <c r="V5" s="2" t="inlineStr"/>
+      <c r="V5" s="3" t="inlineStr">
+        <is>
+          <t>verification: dropout, suspects, and ω all within thresholds</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1031,9 +1021,9 @@
       <c r="F6" t="n">
         <v>1.725</v>
       </c>
-      <c r="G6" s="6" t="inlineStr">
-        <is>
-          <t>TRACKED — verify pending</t>
+      <c r="G6" s="7" t="inlineStr">
+        <is>
+          <t>DONE ✅</t>
         </is>
       </c>
       <c r="H6" t="n">
@@ -1048,47 +1038,47 @@
       <c r="K6" t="n">
         <v>1075</v>
       </c>
-      <c r="L6" s="2" t="inlineStr">
+      <c r="L6" s="3" t="inlineStr">
         <is>
           <t>none</t>
         </is>
       </c>
-      <c r="M6" s="5" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="N6" s="3" t="inlineStr">
-        <is>
-          <t>❌</t>
-        </is>
-      </c>
-      <c r="O6" s="5" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="P6" s="5" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="Q6" s="5" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="R6" s="5" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="S6" s="5" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="T6" s="5" t="inlineStr">
+      <c r="M6" s="4" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="N6" s="4" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="O6" s="4" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="P6" s="4" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="Q6" s="4" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="R6" s="4" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="S6" s="4" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="T6" s="4" t="inlineStr">
         <is>
           <t>✅</t>
         </is>
@@ -1098,7 +1088,11 @@
           <t>global</t>
         </is>
       </c>
-      <c r="V6" s="2" t="inlineStr"/>
+      <c r="V6" s="3" t="inlineStr">
+        <is>
+          <t>verification: verify_tracking.py @ 2500 deg/s cap: 0 dropouts, 0 suspects across 1239 frames (164 holding, 1075 free_swing). All physics plausible.</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1120,87 +1114,83 @@
         <v>1</v>
       </c>
       <c r="E7" t="n">
-        <v>46.77</v>
+        <v>45.25</v>
       </c>
       <c r="F7" t="n">
-        <v>-2.36</v>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M7" s="3" t="inlineStr">
-        <is>
-          <t>❌</t>
-        </is>
-      </c>
-      <c r="N7" s="3" t="inlineStr">
-        <is>
-          <t>❌</t>
-        </is>
-      </c>
-      <c r="O7" s="3" t="inlineStr">
-        <is>
-          <t>❌</t>
-        </is>
-      </c>
-      <c r="P7" s="3" t="inlineStr">
-        <is>
-          <t>❌</t>
-        </is>
-      </c>
-      <c r="Q7" s="3" t="inlineStr">
-        <is>
-          <t>❌</t>
-        </is>
-      </c>
-      <c r="R7" s="3" t="inlineStr">
-        <is>
-          <t>❌</t>
-        </is>
-      </c>
-      <c r="S7" s="3" t="inlineStr">
-        <is>
-          <t>❌</t>
-        </is>
-      </c>
-      <c r="T7" s="3" t="inlineStr">
+        <v>-0.699</v>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>TRACKED — analysis pending</t>
+        </is>
+      </c>
+      <c r="H7" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="K7" t="n">
+        <v>2652</v>
+      </c>
+      <c r="L7" s="3" t="inlineStr">
+        <is>
+          <t>4 runs: f261 (4.4s, isolated) | f265 (4.4s, isolated) | f268–f272 (4.5s–4.5s, 0.1s) | f298–f304 (5.0s–5.1s, 0.1s)</t>
+        </is>
+      </c>
+      <c r="M7" s="4" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="N7" s="4" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="O7" s="5" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="P7" s="5" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="Q7" s="5" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="R7" s="5" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="S7" s="5" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="T7" s="5" t="inlineStr">
         <is>
           <t>❌</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>global</t>
-        </is>
-      </c>
-      <c r="V7" s="2" t="inlineStr"/>
+          <t>per-video</t>
+        </is>
+      </c>
+      <c r="V7" s="3" t="inlineStr">
+        <is>
+          <t>verification: PASS via manual_correction strict-physics flow.</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1222,87 +1212,83 @@
         <v>1</v>
       </c>
       <c r="E8" t="n">
-        <v>55.91</v>
+        <v>55.037</v>
       </c>
       <c r="F8" t="n">
-        <v>-1</v>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M8" s="3" t="inlineStr">
-        <is>
-          <t>❌</t>
-        </is>
-      </c>
-      <c r="N8" s="3" t="inlineStr">
-        <is>
-          <t>❌</t>
-        </is>
-      </c>
-      <c r="O8" s="3" t="inlineStr">
-        <is>
-          <t>❌</t>
-        </is>
-      </c>
-      <c r="P8" s="3" t="inlineStr">
-        <is>
-          <t>❌</t>
-        </is>
-      </c>
-      <c r="Q8" s="3" t="inlineStr">
-        <is>
-          <t>❌</t>
-        </is>
-      </c>
-      <c r="R8" s="3" t="inlineStr">
-        <is>
-          <t>❌</t>
-        </is>
-      </c>
-      <c r="S8" s="3" t="inlineStr">
-        <is>
-          <t>❌</t>
-        </is>
-      </c>
-      <c r="T8" s="3" t="inlineStr">
+        <v>-2.108</v>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>TRACKED — analysis pending</t>
+        </is>
+      </c>
+      <c r="H8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" t="n">
+        <v>1512</v>
+      </c>
+      <c r="L8" s="3" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="M8" s="4" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="N8" s="4" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="O8" s="5" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="P8" s="5" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="Q8" s="5" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="R8" s="5" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="S8" s="5" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="T8" s="5" t="inlineStr">
         <is>
           <t>❌</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>global</t>
-        </is>
-      </c>
-      <c r="V8" s="2" t="inlineStr"/>
+          <t>per-video</t>
+        </is>
+      </c>
+      <c r="V8" s="3" t="inlineStr">
+        <is>
+          <t>verification: dropout, suspects, and ω all within thresholds</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1324,281 +1310,267 @@
         <v>1</v>
       </c>
       <c r="E9" t="n">
-        <v>67.13</v>
+        <v>68.199</v>
       </c>
       <c r="F9" t="n">
-        <v>95.92</v>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M9" s="3" t="inlineStr">
-        <is>
-          <t>❌</t>
-        </is>
-      </c>
-      <c r="N9" s="3" t="inlineStr">
-        <is>
-          <t>❌</t>
-        </is>
-      </c>
-      <c r="O9" s="3" t="inlineStr">
-        <is>
-          <t>❌</t>
-        </is>
-      </c>
-      <c r="P9" s="3" t="inlineStr">
-        <is>
-          <t>❌</t>
-        </is>
-      </c>
-      <c r="Q9" s="3" t="inlineStr">
-        <is>
-          <t>❌</t>
-        </is>
-      </c>
-      <c r="R9" s="3" t="inlineStr">
-        <is>
-          <t>❌</t>
-        </is>
-      </c>
-      <c r="S9" s="3" t="inlineStr">
-        <is>
-          <t>❌</t>
-        </is>
-      </c>
-      <c r="T9" s="3" t="inlineStr">
+        <v>90.60299999999999</v>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>TRACKED — analysis pending</t>
+        </is>
+      </c>
+      <c r="H9" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" t="n">
+        <v>1438</v>
+      </c>
+      <c r="L9" s="3" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="M9" s="4" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="N9" s="4" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="O9" s="5" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="P9" s="5" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="Q9" s="5" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="R9" s="5" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="S9" s="5" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="T9" s="5" t="inlineStr">
         <is>
           <t>❌</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>global</t>
-        </is>
-      </c>
-      <c r="V9" s="2" t="inlineStr"/>
+          <t>per-video</t>
+        </is>
+      </c>
+      <c r="V9" s="3" t="inlineStr">
+        <is>
+          <t>verification: PASS via WARN-band manual triage 2026-05-01. Smooth coupled oscillation over 24s, 0 hidden suspects, 4.3% dropout entirely in holding phase. Peak |omega2|=2402 is one early-release spike, otherwise within physical bounds.</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>th1_p079_th2_p000</t>
+          <t>th1_p090_th2_p000_r2</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>DSC_0141</t>
+          <t>th1_p090_th2_p000_r2</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>th1_p079_th2_p000.mov</t>
+          <t>th1_p090_th2_p000_2.mov</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E10" t="n">
-        <v>78.69</v>
+        <v>71.67700000000001</v>
       </c>
       <c r="F10" t="n">
-        <v>0.35</v>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M10" s="3" t="inlineStr">
-        <is>
-          <t>❌</t>
-        </is>
-      </c>
-      <c r="N10" s="3" t="inlineStr">
-        <is>
-          <t>❌</t>
-        </is>
-      </c>
-      <c r="O10" s="3" t="inlineStr">
-        <is>
-          <t>❌</t>
-        </is>
-      </c>
-      <c r="P10" s="3" t="inlineStr">
-        <is>
-          <t>❌</t>
-        </is>
-      </c>
-      <c r="Q10" s="3" t="inlineStr">
-        <is>
-          <t>❌</t>
-        </is>
-      </c>
-      <c r="R10" s="3" t="inlineStr">
-        <is>
-          <t>❌</t>
-        </is>
-      </c>
-      <c r="S10" s="3" t="inlineStr">
-        <is>
-          <t>❌</t>
-        </is>
-      </c>
-      <c r="T10" s="3" t="inlineStr">
+        <v>-82.26600000000001</v>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>TRACKED — analysis pending</t>
+        </is>
+      </c>
+      <c r="H10" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="I10" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="J10" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="K10" t="n">
+        <v>2681</v>
+      </c>
+      <c r="L10" s="3" t="inlineStr">
+        <is>
+          <t>23 runs (top 5 by duration): f455–f459 (7.6s–7.7s, 0.1s) | f85–f88 (1.4s–1.5s, 0.1s) | f222–f224 (3.7s–3.7s, 0.0s) | f259–f260 (4.3s–4.3s, 0.0s) | f523–f524 (8.7s–8.7s, 0.0s) ... and 18 more</t>
+        </is>
+      </c>
+      <c r="M10" s="4" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="N10" s="4" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="O10" s="5" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="P10" s="5" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="Q10" s="5" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="R10" s="5" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="S10" s="5" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="T10" s="5" t="inlineStr">
         <is>
           <t>❌</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>global</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="inlineStr"/>
+          <t>per-video</t>
+        </is>
+      </c>
+      <c r="V10" s="3" t="inlineStr">
+        <is>
+          <t>Repeat trial of th1_p090_th2_p000. Registered during measurements/ migration.
+⚠ repeat trial
+verification: manually accepted via chaos next</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>th1_p082_th2_p001</t>
+          <t>th1_p079_th2_p000</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>th1_p082_th2_p001</t>
+          <t>DSC_0141</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>th1_p082_th2_p001.mov</t>
+          <t>th1_p079_th2_p000.mov</t>
         </is>
       </c>
       <c r="D11" t="n">
         <v>1</v>
       </c>
       <c r="E11" t="n">
-        <v>81.72</v>
+        <v>78.27500000000001</v>
       </c>
       <c r="F11" t="n">
-        <v>0.73</v>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M11" s="3" t="inlineStr">
-        <is>
-          <t>❌</t>
-        </is>
-      </c>
-      <c r="N11" s="3" t="inlineStr">
-        <is>
-          <t>❌</t>
-        </is>
-      </c>
-      <c r="O11" s="3" t="inlineStr">
-        <is>
-          <t>❌</t>
-        </is>
-      </c>
-      <c r="P11" s="3" t="inlineStr">
-        <is>
-          <t>❌</t>
-        </is>
-      </c>
-      <c r="Q11" s="3" t="inlineStr">
-        <is>
-          <t>❌</t>
-        </is>
-      </c>
-      <c r="R11" s="3" t="inlineStr">
-        <is>
-          <t>❌</t>
-        </is>
-      </c>
-      <c r="S11" s="3" t="inlineStr">
-        <is>
-          <t>❌</t>
-        </is>
-      </c>
-      <c r="T11" s="3" t="inlineStr">
+        <v>88.127</v>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>TRACKED — analysis pending</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="n">
+        <v>5.62</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="J11" t="n">
+        <v>5.06</v>
+      </c>
+      <c r="K11" t="n">
+        <v>178</v>
+      </c>
+      <c r="L11" s="3" t="inlineStr">
+        <is>
+          <t>1 run: f250–f259 (4.2s–4.3s, 0.2s)</t>
+        </is>
+      </c>
+      <c r="M11" s="4" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="N11" s="4" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="O11" s="5" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="P11" s="5" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="Q11" s="5" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="R11" s="5" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="S11" s="5" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="T11" s="5" t="inlineStr">
         <is>
           <t>❌</t>
         </is>
@@ -1608,308 +1580,291 @@
           <t>global</t>
         </is>
       </c>
-      <c r="V11" s="2" t="inlineStr"/>
+      <c r="V11" s="3" t="inlineStr">
+        <is>
+          <t>⚠ no per-video HSV calibration</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>th1_p090_th2_p000</t>
+          <t>th1_p082_th2_p001</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>DSC_0160</t>
+          <t>th1_p082_th2_p001</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>th1_p090_th2_p000.mov</t>
+          <t>th1_p082_th2_p001.mov</t>
         </is>
       </c>
       <c r="D12" t="n">
         <v>1</v>
       </c>
       <c r="E12" t="n">
-        <v>90.36</v>
+        <v>81.81999999999999</v>
       </c>
       <c r="F12" t="n">
+        <v>-0.345</v>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>TRACKED — analysis pending</t>
+        </is>
+      </c>
+      <c r="H12" t="n">
         <v>0</v>
       </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M12" s="3" t="inlineStr">
-        <is>
-          <t>❌</t>
-        </is>
-      </c>
-      <c r="N12" s="3" t="inlineStr">
-        <is>
-          <t>❌</t>
-        </is>
-      </c>
-      <c r="O12" s="3" t="inlineStr">
-        <is>
-          <t>❌</t>
-        </is>
-      </c>
-      <c r="P12" s="3" t="inlineStr">
-        <is>
-          <t>❌</t>
-        </is>
-      </c>
-      <c r="Q12" s="3" t="inlineStr">
-        <is>
-          <t>❌</t>
-        </is>
-      </c>
-      <c r="R12" s="3" t="inlineStr">
-        <is>
-          <t>❌</t>
-        </is>
-      </c>
-      <c r="S12" s="3" t="inlineStr">
-        <is>
-          <t>❌</t>
-        </is>
-      </c>
-      <c r="T12" s="3" t="inlineStr">
+      <c r="I12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" t="n">
+        <v>1573</v>
+      </c>
+      <c r="L12" s="3" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="M12" s="4" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="N12" s="4" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="O12" s="5" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="P12" s="5" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="Q12" s="5" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="R12" s="5" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="S12" s="5" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="T12" s="5" t="inlineStr">
         <is>
           <t>❌</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>global</t>
-        </is>
-      </c>
-      <c r="V12" s="2" t="inlineStr"/>
+          <t>per-video</t>
+        </is>
+      </c>
+      <c r="V12" s="3" t="inlineStr">
+        <is>
+          <t>verification: dropout, suspects, and ω all within thresholds</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>th1_p090_th2_p000_r2</t>
+          <t>th1_p091_th2_m001</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>th1_p090_th2_p000_r2</t>
+          <t>DSC_0162</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>th1_p090_th2_p000_2.mov</t>
+          <t>th1_p091_th2_m001.mov</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E13" t="n">
-        <v>90.36</v>
+        <v>90.354</v>
       </c>
       <c r="F13" t="n">
+        <v>-1.406</v>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>TRACKED — analysis pending</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="n">
+        <v>5.77</v>
+      </c>
+      <c r="I13" t="n">
         <v>0</v>
       </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M13" s="3" t="inlineStr">
-        <is>
-          <t>❌</t>
-        </is>
-      </c>
-      <c r="N13" s="3" t="inlineStr">
-        <is>
-          <t>❌</t>
-        </is>
-      </c>
-      <c r="O13" s="3" t="inlineStr">
-        <is>
-          <t>❌</t>
-        </is>
-      </c>
-      <c r="P13" s="3" t="inlineStr">
-        <is>
-          <t>❌</t>
-        </is>
-      </c>
-      <c r="Q13" s="3" t="inlineStr">
-        <is>
-          <t>❌</t>
-        </is>
-      </c>
-      <c r="R13" s="3" t="inlineStr">
-        <is>
-          <t>❌</t>
-        </is>
-      </c>
-      <c r="S13" s="3" t="inlineStr">
-        <is>
-          <t>❌</t>
-        </is>
-      </c>
-      <c r="T13" s="3" t="inlineStr">
+      <c r="J13" t="n">
+        <v>5.77</v>
+      </c>
+      <c r="K13" t="n">
+        <v>1958</v>
+      </c>
+      <c r="L13" s="3" t="inlineStr">
+        <is>
+          <t>10 runs: f115 (1.9s, isolated) | f146–f147 (2.4s–2.5s, 0.0s) | f157–f161 (2.6s–2.7s, 0.1s) | f163 (2.7s, isolated) | f165–f166 (2.8s–2.8s, 0.0s) | f196 (3.3s, isolated) | f198–f250 (3.3s–4.2s, 0.9s) | f252–f291 (4.2s–4.9s, 0.7s) | f293–f299 (4.9s–5.0s, 0.1s) | f301 (5.0s, isolated)</t>
+        </is>
+      </c>
+      <c r="M13" s="4" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="N13" s="4" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="O13" s="5" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="P13" s="5" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="Q13" s="5" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="R13" s="5" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="S13" s="5" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="T13" s="5" t="inlineStr">
         <is>
           <t>❌</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>global</t>
-        </is>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>Repeat trial of th1_p090_th2_p000. Registered during measurements/ migration.
-⚠ repeat trial</t>
+          <t>per-video</t>
+        </is>
+      </c>
+      <c r="V13" s="3" t="inlineStr">
+        <is>
+          <t>verification: PASS via WARN-band manual triage 2026-05-01. Smooth coupled oscillation over 33s, 0 hidden suspects, 9.6% dropout entirely in holding phase. Tracked via manual_correction; registry dropout_rate_pct field is stale — see verification.csv for ground truth.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>th1_p091_th2_m001</t>
+          <t>th1_p090_th2_p000</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>DSC_0162</t>
+          <t>DSC_0160</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>th1_p091_th2_m001.mov</t>
+          <t>th1_p090_th2_p000.mov</t>
         </is>
       </c>
       <c r="D14" t="n">
         <v>1</v>
       </c>
       <c r="E14" t="n">
-        <v>90.70999999999999</v>
+        <v>91.06100000000001</v>
       </c>
       <c r="F14" t="n">
-        <v>-1.41</v>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M14" s="3" t="inlineStr">
-        <is>
-          <t>❌</t>
-        </is>
-      </c>
-      <c r="N14" s="3" t="inlineStr">
-        <is>
-          <t>❌</t>
-        </is>
-      </c>
-      <c r="O14" s="3" t="inlineStr">
-        <is>
-          <t>❌</t>
-        </is>
-      </c>
-      <c r="P14" s="3" t="inlineStr">
-        <is>
-          <t>❌</t>
-        </is>
-      </c>
-      <c r="Q14" s="3" t="inlineStr">
-        <is>
-          <t>❌</t>
-        </is>
-      </c>
-      <c r="R14" s="3" t="inlineStr">
-        <is>
-          <t>❌</t>
-        </is>
-      </c>
-      <c r="S14" s="3" t="inlineStr">
-        <is>
-          <t>❌</t>
-        </is>
-      </c>
-      <c r="T14" s="3" t="inlineStr">
+        <v>1.414</v>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>TRACKED — analysis pending</t>
+        </is>
+      </c>
+      <c r="H14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" t="n">
+        <v>88</v>
+      </c>
+      <c r="L14" s="3" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="M14" s="4" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="N14" s="4" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="O14" s="5" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="P14" s="5" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="Q14" s="5" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="R14" s="5" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="S14" s="5" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="T14" s="5" t="inlineStr">
         <is>
           <t>❌</t>
         </is>
@@ -1919,7 +1874,7 @@
           <t>global</t>
         </is>
       </c>
-      <c r="V14" s="2" t="inlineStr"/>
+      <c r="V14" s="3" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1971,57 +1926,57 @@
           <t>—</t>
         </is>
       </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M15" s="3" t="inlineStr">
-        <is>
-          <t>❌</t>
-        </is>
-      </c>
-      <c r="N15" s="3" t="inlineStr">
-        <is>
-          <t>❌</t>
-        </is>
-      </c>
-      <c r="O15" s="3" t="inlineStr">
-        <is>
-          <t>❌</t>
-        </is>
-      </c>
-      <c r="P15" s="3" t="inlineStr">
-        <is>
-          <t>❌</t>
-        </is>
-      </c>
-      <c r="Q15" s="3" t="inlineStr">
-        <is>
-          <t>❌</t>
-        </is>
-      </c>
-      <c r="R15" s="3" t="inlineStr">
-        <is>
-          <t>❌</t>
-        </is>
-      </c>
-      <c r="S15" s="3" t="inlineStr">
-        <is>
-          <t>❌</t>
-        </is>
-      </c>
-      <c r="T15" s="3" t="inlineStr">
+      <c r="L15" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M15" s="5" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="N15" s="5" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="O15" s="5" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="P15" s="5" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="Q15" s="5" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="R15" s="5" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="S15" s="5" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="T15" s="5" t="inlineStr">
         <is>
           <t>❌</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
         <is>
-          <t>global</t>
-        </is>
-      </c>
-      <c r="V15" s="2" t="inlineStr"/>
+          <t>per-video</t>
+        </is>
+      </c>
+      <c r="V15" s="3" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -2073,47 +2028,47 @@
           <t>—</t>
         </is>
       </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M16" s="3" t="inlineStr">
-        <is>
-          <t>❌</t>
-        </is>
-      </c>
-      <c r="N16" s="3" t="inlineStr">
-        <is>
-          <t>❌</t>
-        </is>
-      </c>
-      <c r="O16" s="3" t="inlineStr">
-        <is>
-          <t>❌</t>
-        </is>
-      </c>
-      <c r="P16" s="3" t="inlineStr">
-        <is>
-          <t>❌</t>
-        </is>
-      </c>
-      <c r="Q16" s="3" t="inlineStr">
-        <is>
-          <t>❌</t>
-        </is>
-      </c>
-      <c r="R16" s="3" t="inlineStr">
-        <is>
-          <t>❌</t>
-        </is>
-      </c>
-      <c r="S16" s="3" t="inlineStr">
-        <is>
-          <t>❌</t>
-        </is>
-      </c>
-      <c r="T16" s="3" t="inlineStr">
+      <c r="L16" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M16" s="5" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="N16" s="5" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="O16" s="5" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="P16" s="5" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="Q16" s="5" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="R16" s="5" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="S16" s="5" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="T16" s="5" t="inlineStr">
         <is>
           <t>❌</t>
         </is>
@@ -2123,7 +2078,7 @@
           <t>global</t>
         </is>
       </c>
-      <c r="V16" s="2" t="inlineStr"/>
+      <c r="V16" s="3" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -2175,47 +2130,47 @@
           <t>—</t>
         </is>
       </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M17" s="3" t="inlineStr">
-        <is>
-          <t>❌</t>
-        </is>
-      </c>
-      <c r="N17" s="3" t="inlineStr">
-        <is>
-          <t>❌</t>
-        </is>
-      </c>
-      <c r="O17" s="3" t="inlineStr">
-        <is>
-          <t>❌</t>
-        </is>
-      </c>
-      <c r="P17" s="3" t="inlineStr">
-        <is>
-          <t>❌</t>
-        </is>
-      </c>
-      <c r="Q17" s="3" t="inlineStr">
-        <is>
-          <t>❌</t>
-        </is>
-      </c>
-      <c r="R17" s="3" t="inlineStr">
-        <is>
-          <t>❌</t>
-        </is>
-      </c>
-      <c r="S17" s="3" t="inlineStr">
-        <is>
-          <t>❌</t>
-        </is>
-      </c>
-      <c r="T17" s="3" t="inlineStr">
+      <c r="L17" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M17" s="5" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="N17" s="5" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="O17" s="5" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="P17" s="5" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="Q17" s="5" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="R17" s="5" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="S17" s="5" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="T17" s="5" t="inlineStr">
         <is>
           <t>❌</t>
         </is>
@@ -2225,7 +2180,7 @@
           <t>global</t>
         </is>
       </c>
-      <c r="V17" s="2" t="inlineStr"/>
+      <c r="V17" s="3" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -2277,47 +2232,47 @@
           <t>—</t>
         </is>
       </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M18" s="3" t="inlineStr">
-        <is>
-          <t>❌</t>
-        </is>
-      </c>
-      <c r="N18" s="3" t="inlineStr">
-        <is>
-          <t>❌</t>
-        </is>
-      </c>
-      <c r="O18" s="3" t="inlineStr">
-        <is>
-          <t>❌</t>
-        </is>
-      </c>
-      <c r="P18" s="3" t="inlineStr">
-        <is>
-          <t>❌</t>
-        </is>
-      </c>
-      <c r="Q18" s="3" t="inlineStr">
-        <is>
-          <t>❌</t>
-        </is>
-      </c>
-      <c r="R18" s="3" t="inlineStr">
-        <is>
-          <t>❌</t>
-        </is>
-      </c>
-      <c r="S18" s="3" t="inlineStr">
-        <is>
-          <t>❌</t>
-        </is>
-      </c>
-      <c r="T18" s="3" t="inlineStr">
+      <c r="L18" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M18" s="5" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="N18" s="5" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="O18" s="5" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="P18" s="5" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="Q18" s="5" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="R18" s="5" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="S18" s="5" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="T18" s="5" t="inlineStr">
         <is>
           <t>❌</t>
         </is>
@@ -2327,7 +2282,7 @@
           <t>global</t>
         </is>
       </c>
-      <c r="V18" s="2" t="inlineStr"/>
+      <c r="V18" s="3" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -2379,47 +2334,47 @@
           <t>—</t>
         </is>
       </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M19" s="3" t="inlineStr">
-        <is>
-          <t>❌</t>
-        </is>
-      </c>
-      <c r="N19" s="3" t="inlineStr">
-        <is>
-          <t>❌</t>
-        </is>
-      </c>
-      <c r="O19" s="3" t="inlineStr">
-        <is>
-          <t>❌</t>
-        </is>
-      </c>
-      <c r="P19" s="3" t="inlineStr">
-        <is>
-          <t>❌</t>
-        </is>
-      </c>
-      <c r="Q19" s="3" t="inlineStr">
-        <is>
-          <t>❌</t>
-        </is>
-      </c>
-      <c r="R19" s="3" t="inlineStr">
-        <is>
-          <t>❌</t>
-        </is>
-      </c>
-      <c r="S19" s="3" t="inlineStr">
-        <is>
-          <t>❌</t>
-        </is>
-      </c>
-      <c r="T19" s="3" t="inlineStr">
+      <c r="L19" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M19" s="5" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="N19" s="5" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="O19" s="5" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="P19" s="5" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="Q19" s="5" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="R19" s="5" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="S19" s="5" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="T19" s="5" t="inlineStr">
         <is>
           <t>❌</t>
         </is>
@@ -2429,7 +2384,7 @@
           <t>global</t>
         </is>
       </c>
-      <c r="V19" s="2" t="inlineStr"/>
+      <c r="V19" s="3" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2481,47 +2436,47 @@
           <t>—</t>
         </is>
       </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M20" s="3" t="inlineStr">
-        <is>
-          <t>❌</t>
-        </is>
-      </c>
-      <c r="N20" s="3" t="inlineStr">
-        <is>
-          <t>❌</t>
-        </is>
-      </c>
-      <c r="O20" s="3" t="inlineStr">
-        <is>
-          <t>❌</t>
-        </is>
-      </c>
-      <c r="P20" s="3" t="inlineStr">
-        <is>
-          <t>❌</t>
-        </is>
-      </c>
-      <c r="Q20" s="3" t="inlineStr">
-        <is>
-          <t>❌</t>
-        </is>
-      </c>
-      <c r="R20" s="3" t="inlineStr">
-        <is>
-          <t>❌</t>
-        </is>
-      </c>
-      <c r="S20" s="3" t="inlineStr">
-        <is>
-          <t>❌</t>
-        </is>
-      </c>
-      <c r="T20" s="3" t="inlineStr">
+      <c r="L20" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M20" s="5" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="N20" s="5" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="O20" s="5" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="P20" s="5" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="Q20" s="5" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="R20" s="5" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="S20" s="5" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="T20" s="5" t="inlineStr">
         <is>
           <t>❌</t>
         </is>
@@ -2531,7 +2486,7 @@
           <t>global</t>
         </is>
       </c>
-      <c r="V20" s="2" t="inlineStr">
+      <c r="V20" s="3" t="inlineStr">
         <is>
           <t>Repeat trial of th1_p094_th2_p000. Registered during measurements/ migration.
 ⚠ repeat trial</t>
@@ -2588,47 +2543,47 @@
           <t>—</t>
         </is>
       </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M21" s="3" t="inlineStr">
-        <is>
-          <t>❌</t>
-        </is>
-      </c>
-      <c r="N21" s="3" t="inlineStr">
-        <is>
-          <t>❌</t>
-        </is>
-      </c>
-      <c r="O21" s="3" t="inlineStr">
-        <is>
-          <t>❌</t>
-        </is>
-      </c>
-      <c r="P21" s="3" t="inlineStr">
-        <is>
-          <t>❌</t>
-        </is>
-      </c>
-      <c r="Q21" s="3" t="inlineStr">
-        <is>
-          <t>❌</t>
-        </is>
-      </c>
-      <c r="R21" s="3" t="inlineStr">
-        <is>
-          <t>❌</t>
-        </is>
-      </c>
-      <c r="S21" s="3" t="inlineStr">
-        <is>
-          <t>❌</t>
-        </is>
-      </c>
-      <c r="T21" s="3" t="inlineStr">
+      <c r="L21" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M21" s="5" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="N21" s="5" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="O21" s="5" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="P21" s="5" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="Q21" s="5" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="R21" s="5" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="S21" s="5" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="T21" s="5" t="inlineStr">
         <is>
           <t>❌</t>
         </is>
@@ -2638,7 +2593,7 @@
           <t>global</t>
         </is>
       </c>
-      <c r="V21" s="2" t="inlineStr"/>
+      <c r="V21" s="3" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2690,47 +2645,47 @@
           <t>—</t>
         </is>
       </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M22" s="3" t="inlineStr">
-        <is>
-          <t>❌</t>
-        </is>
-      </c>
-      <c r="N22" s="3" t="inlineStr">
-        <is>
-          <t>❌</t>
-        </is>
-      </c>
-      <c r="O22" s="3" t="inlineStr">
-        <is>
-          <t>❌</t>
-        </is>
-      </c>
-      <c r="P22" s="3" t="inlineStr">
-        <is>
-          <t>❌</t>
-        </is>
-      </c>
-      <c r="Q22" s="3" t="inlineStr">
-        <is>
-          <t>❌</t>
-        </is>
-      </c>
-      <c r="R22" s="3" t="inlineStr">
-        <is>
-          <t>❌</t>
-        </is>
-      </c>
-      <c r="S22" s="3" t="inlineStr">
-        <is>
-          <t>❌</t>
-        </is>
-      </c>
-      <c r="T22" s="3" t="inlineStr">
+      <c r="L22" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M22" s="5" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="N22" s="5" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="O22" s="5" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="P22" s="5" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="Q22" s="5" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="R22" s="5" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="S22" s="5" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="T22" s="5" t="inlineStr">
         <is>
           <t>❌</t>
         </is>
@@ -2740,7 +2695,7 @@
           <t>global</t>
         </is>
       </c>
-      <c r="V22" s="2" t="inlineStr"/>
+      <c r="V22" s="3" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2792,47 +2747,47 @@
           <t>—</t>
         </is>
       </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M23" s="3" t="inlineStr">
-        <is>
-          <t>❌</t>
-        </is>
-      </c>
-      <c r="N23" s="3" t="inlineStr">
-        <is>
-          <t>❌</t>
-        </is>
-      </c>
-      <c r="O23" s="3" t="inlineStr">
-        <is>
-          <t>❌</t>
-        </is>
-      </c>
-      <c r="P23" s="3" t="inlineStr">
-        <is>
-          <t>❌</t>
-        </is>
-      </c>
-      <c r="Q23" s="3" t="inlineStr">
-        <is>
-          <t>❌</t>
-        </is>
-      </c>
-      <c r="R23" s="3" t="inlineStr">
-        <is>
-          <t>❌</t>
-        </is>
-      </c>
-      <c r="S23" s="3" t="inlineStr">
-        <is>
-          <t>❌</t>
-        </is>
-      </c>
-      <c r="T23" s="3" t="inlineStr">
+      <c r="L23" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M23" s="5" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="N23" s="5" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="O23" s="5" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="P23" s="5" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="Q23" s="5" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="R23" s="5" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="S23" s="5" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="T23" s="5" t="inlineStr">
         <is>
           <t>❌</t>
         </is>
@@ -2842,7 +2797,7 @@
           <t>global</t>
         </is>
       </c>
-      <c r="V23" s="2" t="inlineStr"/>
+      <c r="V23" s="3" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2869,82 +2824,74 @@
       <c r="F24" t="n">
         <v>90.34999999999999</v>
       </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M24" s="3" t="inlineStr">
-        <is>
-          <t>❌</t>
-        </is>
-      </c>
-      <c r="N24" s="3" t="inlineStr">
-        <is>
-          <t>❌</t>
-        </is>
-      </c>
-      <c r="O24" s="3" t="inlineStr">
-        <is>
-          <t>❌</t>
-        </is>
-      </c>
-      <c r="P24" s="3" t="inlineStr">
-        <is>
-          <t>❌</t>
-        </is>
-      </c>
-      <c r="Q24" s="3" t="inlineStr">
-        <is>
-          <t>❌</t>
-        </is>
-      </c>
-      <c r="R24" s="3" t="inlineStr">
-        <is>
-          <t>❌</t>
-        </is>
-      </c>
-      <c r="S24" s="3" t="inlineStr">
-        <is>
-          <t>❌</t>
-        </is>
-      </c>
-      <c r="T24" s="3" t="inlineStr">
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>TRACKED — analysis pending</t>
+        </is>
+      </c>
+      <c r="H24" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="I24" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="J24" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="K24" t="n">
+        <v>672</v>
+      </c>
+      <c r="L24" s="3" t="inlineStr">
+        <is>
+          <t>5 isolated frames</t>
+        </is>
+      </c>
+      <c r="M24" s="4" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="N24" s="5" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="O24" s="5" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="P24" s="5" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="Q24" s="5" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="R24" s="5" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="S24" s="5" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="T24" s="5" t="inlineStr">
         <is>
           <t>❌</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
         <is>
-          <t>global</t>
-        </is>
-      </c>
-      <c r="V24" s="2" t="inlineStr"/>
+          <t>per-video</t>
+        </is>
+      </c>
+      <c r="V24" s="3" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2966,87 +2913,79 @@
         <v>1</v>
       </c>
       <c r="E25" t="n">
-        <v>160.37</v>
+        <v>155.469</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.7</v>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L25" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M25" s="3" t="inlineStr">
-        <is>
-          <t>❌</t>
-        </is>
-      </c>
-      <c r="N25" s="3" t="inlineStr">
-        <is>
-          <t>❌</t>
-        </is>
-      </c>
-      <c r="O25" s="3" t="inlineStr">
-        <is>
-          <t>❌</t>
-        </is>
-      </c>
-      <c r="P25" s="3" t="inlineStr">
-        <is>
-          <t>❌</t>
-        </is>
-      </c>
-      <c r="Q25" s="3" t="inlineStr">
-        <is>
-          <t>❌</t>
-        </is>
-      </c>
-      <c r="R25" s="3" t="inlineStr">
-        <is>
-          <t>❌</t>
-        </is>
-      </c>
-      <c r="S25" s="3" t="inlineStr">
-        <is>
-          <t>❌</t>
-        </is>
-      </c>
-      <c r="T25" s="3" t="inlineStr">
+        <v>-16.699</v>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>TRACKED — analysis pending</t>
+        </is>
+      </c>
+      <c r="H25" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="I25" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="J25" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="K25" t="n">
+        <v>1888</v>
+      </c>
+      <c r="L25" s="3" t="inlineStr">
+        <is>
+          <t>27 runs (top 5 by duration): f1787–f1789 (29.8s–29.8s, 0.0s) | f259–f260 (4.3s–4.3s, 0.0s) | f385–f386 (6.4s–6.4s, 0.0s) | f1039–f1040 (17.3s–17.4s, 0.0s) | f1505–f1506 (25.1s–25.1s, 0.0s) ... and 22 more</t>
+        </is>
+      </c>
+      <c r="M25" s="4" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="N25" s="4" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="O25" s="5" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="P25" s="5" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="Q25" s="5" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="R25" s="5" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="S25" s="5" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="T25" s="5" t="inlineStr">
         <is>
           <t>❌</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
         <is>
-          <t>global</t>
-        </is>
-      </c>
-      <c r="V25" s="2" t="inlineStr"/>
+          <t>per-video</t>
+        </is>
+      </c>
+      <c r="V25" s="3" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -3098,141 +3037,141 @@
           <t>—</t>
         </is>
       </c>
-      <c r="L26" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M26" s="3" t="inlineStr">
-        <is>
-          <t>❌</t>
-        </is>
-      </c>
-      <c r="N26" s="3" t="inlineStr">
-        <is>
-          <t>❌</t>
-        </is>
-      </c>
-      <c r="O26" s="3" t="inlineStr">
-        <is>
-          <t>❌</t>
-        </is>
-      </c>
-      <c r="P26" s="3" t="inlineStr">
-        <is>
-          <t>❌</t>
-        </is>
-      </c>
-      <c r="Q26" s="3" t="inlineStr">
-        <is>
-          <t>❌</t>
-        </is>
-      </c>
-      <c r="R26" s="3" t="inlineStr">
-        <is>
-          <t>❌</t>
-        </is>
-      </c>
-      <c r="S26" s="3" t="inlineStr">
-        <is>
-          <t>❌</t>
-        </is>
-      </c>
-      <c r="T26" s="3" t="inlineStr">
+      <c r="L26" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M26" s="5" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="N26" s="5" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="O26" s="5" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="P26" s="5" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="Q26" s="5" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="R26" s="5" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="S26" s="5" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="T26" s="5" t="inlineStr">
         <is>
           <t>❌</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
         <is>
-          <t>global</t>
-        </is>
-      </c>
-      <c r="V26" s="2" t="inlineStr"/>
+          <t>per-video</t>
+        </is>
+      </c>
+      <c r="V26" s="3" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>th1_p180_th2_p180</t>
+          <t>th1_p180_th2_p090</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>th1_p180_th2_p180</t>
+          <t>DSC_0146</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>th1_p180_th2_p180.mov</t>
+          <t>th1_p180_th2_p090.mov</t>
         </is>
       </c>
       <c r="D27" t="n">
         <v>1</v>
       </c>
       <c r="E27" t="n">
-        <v>178.577</v>
+        <v>176.915</v>
       </c>
       <c r="F27" t="n">
-        <v>105.081</v>
-      </c>
-      <c r="G27" s="6" t="inlineStr">
+        <v>67.116</v>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
         <is>
           <t>TRACKED — analysis pending</t>
         </is>
       </c>
-      <c r="H27" s="6" t="n">
-        <v>5.04</v>
+      <c r="H27" t="n">
+        <v>1.09</v>
       </c>
       <c r="I27" t="n">
-        <v>0</v>
+        <v>0.97</v>
       </c>
       <c r="J27" t="n">
-        <v>5.04</v>
+        <v>1.09</v>
       </c>
       <c r="K27" t="n">
-        <v>1390</v>
-      </c>
-      <c r="L27" s="2" t="inlineStr">
-        <is>
-          <t>12 runs (top 5 by duration): f126–f143 (2.1s–2.4s, 0.3s) | f88–f101 (1.5s–1.7s, 0.2s) | f103–f113 (1.7s–1.9s, 0.2s) | f382–f388 (6.4s–6.5s, 0.1s) | f77–f81 (1.3s–1.4s, 0.1s) ... and 7 more</t>
-        </is>
-      </c>
-      <c r="M27" s="5" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="N27" s="3" t="inlineStr">
-        <is>
-          <t>❌</t>
+        <v>1652</v>
+      </c>
+      <c r="L27" s="3" t="inlineStr">
+        <is>
+          <t>17 runs (top 5 by duration): f129–f130 (2.2s–2.2s, 0.0s) | f427 (7.1s, isolated) | f511 (8.5s, isolated) | f556 (9.3s, isolated) | f562 (9.4s, isolated) ... and 12 more</t>
+        </is>
+      </c>
+      <c r="M27" s="4" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="N27" s="4" t="inlineStr">
+        <is>
+          <t>✅</t>
         </is>
       </c>
       <c r="O27" s="5" t="inlineStr">
         <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="P27" s="3" t="inlineStr">
-        <is>
-          <t>❌</t>
-        </is>
-      </c>
-      <c r="Q27" s="3" t="inlineStr">
-        <is>
-          <t>❌</t>
-        </is>
-      </c>
-      <c r="R27" s="3" t="inlineStr">
-        <is>
-          <t>❌</t>
-        </is>
-      </c>
-      <c r="S27" s="3" t="inlineStr">
-        <is>
-          <t>❌</t>
-        </is>
-      </c>
-      <c r="T27" s="3" t="inlineStr">
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="P27" s="5" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="Q27" s="5" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="R27" s="5" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="S27" s="5" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="T27" s="5" t="inlineStr">
         <is>
           <t>❌</t>
         </is>
@@ -3242,109 +3181,105 @@
           <t>per-video</t>
         </is>
       </c>
-      <c r="V27" s="2" t="inlineStr"/>
+      <c r="V27" s="3" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>th1_p180_th2_p090</t>
+          <t>th1_p180_th2_p180</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>DSC_0146</t>
+          <t>th1_p180_th2_p180</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>th1_p180_th2_p090.mov</t>
+          <t>th1_p180_th2_p180.mov</t>
         </is>
       </c>
       <c r="D28" t="n">
         <v>1</v>
       </c>
       <c r="E28" t="n">
-        <v>179.65</v>
+        <v>178.577</v>
       </c>
       <c r="F28" t="n">
-        <v>90</v>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L28" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M28" s="3" t="inlineStr">
-        <is>
-          <t>❌</t>
-        </is>
-      </c>
-      <c r="N28" s="3" t="inlineStr">
-        <is>
-          <t>❌</t>
-        </is>
-      </c>
-      <c r="O28" s="3" t="inlineStr">
-        <is>
-          <t>❌</t>
-        </is>
-      </c>
-      <c r="P28" s="3" t="inlineStr">
-        <is>
-          <t>❌</t>
-        </is>
-      </c>
-      <c r="Q28" s="3" t="inlineStr">
-        <is>
-          <t>❌</t>
-        </is>
-      </c>
-      <c r="R28" s="3" t="inlineStr">
-        <is>
-          <t>❌</t>
-        </is>
-      </c>
-      <c r="S28" s="3" t="inlineStr">
-        <is>
-          <t>❌</t>
-        </is>
-      </c>
-      <c r="T28" s="3" t="inlineStr">
-        <is>
-          <t>❌</t>
+        <v>105.081</v>
+      </c>
+      <c r="G28" s="7" t="inlineStr">
+        <is>
+          <t>DONE ✅</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="n">
+        <v>5.04</v>
+      </c>
+      <c r="I28" t="n">
+        <v>0</v>
+      </c>
+      <c r="J28" t="n">
+        <v>5.04</v>
+      </c>
+      <c r="K28" t="n">
+        <v>1390</v>
+      </c>
+      <c r="L28" s="3" t="inlineStr">
+        <is>
+          <t>12 runs (top 5 by duration): f126–f143 (2.1s–2.4s, 0.3s) | f88–f101 (1.5s–1.7s, 0.2s) | f103–f113 (1.7s–1.9s, 0.2s) | f382–f388 (6.4s–6.5s, 0.1s) | f77–f81 (1.3s–1.4s, 0.1s) ... and 7 more</t>
+        </is>
+      </c>
+      <c r="M28" s="4" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="N28" s="4" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="O28" s="4" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="P28" s="4" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="Q28" s="4" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="R28" s="4" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="S28" s="4" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="T28" s="4" t="inlineStr">
+        <is>
+          <t>✅</t>
         </is>
       </c>
       <c r="U28" t="inlineStr">
         <is>
-          <t>global</t>
-        </is>
-      </c>
-      <c r="V28" s="2" t="inlineStr"/>
+          <t>per-video</t>
+        </is>
+      </c>
+      <c r="V28" s="3" t="inlineStr">
+        <is>
+          <t>verification: verify_tracking.py @ 2500 deg/s cap: 70 dropouts (4.98%, mostly early high-energy frames), 2 suspect frames interpolated, 0 suspects after re-verification.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:V28"/>
@@ -3546,9 +3481,9 @@
       <c r="F2" t="n">
         <v>62.074</v>
       </c>
-      <c r="G2" s="7" t="inlineStr">
-        <is>
-          <t>IN PROGRESS (5/8)</t>
+      <c r="G2" s="8" t="inlineStr">
+        <is>
+          <t>IN PROGRESS (6/8)</t>
         </is>
       </c>
       <c r="H2" t="n">
@@ -3563,49 +3498,49 @@
       <c r="K2" t="n">
         <v>30897</v>
       </c>
-      <c r="L2" s="2" t="inlineStr">
+      <c r="L2" s="3" t="inlineStr">
         <is>
           <t>1 isolated frame</t>
         </is>
       </c>
-      <c r="M2" s="5" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="N2" s="5" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="O2" s="3" t="inlineStr">
-        <is>
-          <t>❌</t>
-        </is>
-      </c>
-      <c r="P2" s="5" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="Q2" s="3" t="inlineStr">
-        <is>
-          <t>❌</t>
-        </is>
-      </c>
-      <c r="R2" s="3" t="inlineStr">
-        <is>
-          <t>❌</t>
-        </is>
-      </c>
-      <c r="S2" s="5" t="inlineStr">
+      <c r="M2" s="4" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="N2" s="4" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="O2" s="4" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="P2" s="4" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="Q2" s="4" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="R2" s="5" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="S2" s="4" t="inlineStr">
         <is>
           <t>✅</t>
         </is>
       </c>
       <c r="T2" s="5" t="inlineStr">
         <is>
-          <t>✅</t>
+          <t>❌</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -3613,10 +3548,9 @@
           <t>global</t>
         </is>
       </c>
-      <c r="V2" s="2" t="inlineStr">
-        <is>
-          <t>⚠ combined.mp4 is suspiciously small (&lt;1 MB)
-verification: verify_tracking.py @ 2500 deg/s cap: 23 suspect frames over 30942 total (0.07%); 21 hidden in free_swing (dropout=0). All flags on arm 2; peak |w2|=10676 deg/s vs ~1500 physical limit, indicating brief tracking glitches not physics. Dropout=1 count: 2 (0.01%). Tracking_quality NOT promoted to verified.</t>
+      <c r="V2" s="3" t="inlineStr">
+        <is>
+          <t>verification: PASS via WARN-band manual triage 2026-05-01. 12 residual suspects post-interpolation are paired-frame artefacts in the first 15s of chaos (0.04% of 30k frames); 0% dropout overall, smooth damping for the remaining ~500s.</t>
         </is>
       </c>
       <c r="W2" t="n">
@@ -3626,7 +3560,7 @@
         <v>30897</v>
       </c>
       <c r="Y2" t="n">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="Z2" t="n">
         <v>13.1371</v>

--- a/data/status_report.xlsx
+++ b/data/status_report.xlsx
@@ -2819,10 +2819,10 @@
         <v>1</v>
       </c>
       <c r="E24" t="n">
-        <v>153.43</v>
+        <v>152.193</v>
       </c>
       <c r="F24" t="n">
-        <v>90.34999999999999</v>
+        <v>74.393</v>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
@@ -2830,20 +2830,20 @@
         </is>
       </c>
       <c r="H24" t="n">
-        <v>0.74</v>
+        <v>0.67</v>
       </c>
       <c r="I24" t="n">
-        <v>0.74</v>
+        <v>0.6</v>
       </c>
       <c r="J24" t="n">
-        <v>0.74</v>
+        <v>0.67</v>
       </c>
       <c r="K24" t="n">
-        <v>672</v>
+        <v>2685</v>
       </c>
       <c r="L24" s="3" t="inlineStr">
         <is>
-          <t>5 isolated frames</t>
+          <t>18 isolated frames</t>
         </is>
       </c>
       <c r="M24" s="4" t="inlineStr">
@@ -2851,9 +2851,9 @@
           <t>✅</t>
         </is>
       </c>
-      <c r="N24" s="5" t="inlineStr">
-        <is>
-          <t>❌</t>
+      <c r="N24" s="4" t="inlineStr">
+        <is>
+          <t>✅</t>
         </is>
       </c>
       <c r="O24" s="5" t="inlineStr">
@@ -3007,49 +3007,41 @@
         <v>1</v>
       </c>
       <c r="E26" t="n">
-        <v>176.38</v>
+        <v>162.667</v>
       </c>
       <c r="F26" t="n">
-        <v>180</v>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>-166.979</v>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>TRACKED — analysis pending</t>
+        </is>
+      </c>
+      <c r="H26" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="I26" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="J26" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="K26" t="n">
+        <v>2112</v>
       </c>
       <c r="L26" s="3" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M26" s="5" t="inlineStr">
-        <is>
-          <t>❌</t>
-        </is>
-      </c>
-      <c r="N26" s="5" t="inlineStr">
-        <is>
-          <t>❌</t>
+          <t>18 isolated frames</t>
+        </is>
+      </c>
+      <c r="M26" s="4" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="N26" s="4" t="inlineStr">
+        <is>
+          <t>✅</t>
         </is>
       </c>
       <c r="O26" s="5" t="inlineStr">

--- a/data/status_report.xlsx
+++ b/data/status_report.xlsx
@@ -753,9 +753,9 @@
           <t>✅</t>
         </is>
       </c>
-      <c r="N3" s="5" t="inlineStr">
-        <is>
-          <t>❌</t>
+      <c r="N3" s="4" t="inlineStr">
+        <is>
+          <t>✅</t>
         </is>
       </c>
       <c r="O3" s="4" t="inlineStr">
@@ -929,20 +929,20 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>1.51</v>
+        <v>1.23</v>
       </c>
       <c r="I5" t="n">
         <v>0.47</v>
       </c>
       <c r="J5" t="n">
-        <v>1.51</v>
+        <v>1.23</v>
       </c>
       <c r="K5" t="n">
         <v>1059</v>
       </c>
       <c r="L5" s="3" t="inlineStr">
         <is>
-          <t>3 runs: f97–f98 (1.6s–1.6s, 0.0s) | f171–f181 (2.9s–3.0s, 0.2s) | f213–f215 (3.6s–3.6s, 0.0s)</t>
+          <t>2 runs: f97–f98 (1.6s–1.6s, 0.0s) | f171–f181 (2.9s–3.0s, 0.2s)</t>
         </is>
       </c>
       <c r="M5" s="4" t="inlineStr">
@@ -992,7 +992,7 @@
       </c>
       <c r="V5" s="3" t="inlineStr">
         <is>
-          <t>verification: dropout, suspects, and ω all within thresholds</t>
+          <t>verification: DOWNGRADED via chaos audit on 2026-05-02: was 'verified'; new verdict WARN. Reasons: 12 residual suspects post-interpolation; 16 arm-length violation(s) (max deviation 27.2%) — tracker latched on wrong object; 12 frame(s) with |Δω| spike (unphysical acceleration)</t>
         </is>
       </c>
     </row>
@@ -1286,7 +1286,7 @@
       </c>
       <c r="V8" s="3" t="inlineStr">
         <is>
-          <t>verification: dropout, suspects, and ω all within thresholds</t>
+          <t>verification: DOWNGRADED via chaos audit on 2026-05-02: was 'verified'; new verdict WARN. Reasons: 1 residual suspects post-interpolation; 1 frame(s) with |Δω| spike (unphysical acceleration)</t>
         </is>
       </c>
     </row>
@@ -1384,7 +1384,7 @@
       </c>
       <c r="V9" s="3" t="inlineStr">
         <is>
-          <t>verification: PASS via WARN-band manual triage 2026-05-01. Smooth coupled oscillation over 24s, 0 hidden suspects, 4.3% dropout entirely in holding phase. Peak |omega2|=2402 is one early-release spike, otherwise within physical bounds.</t>
+          <t>verification: DOWNGRADED via chaos audit on 2026-05-02: was 'verified'; new verdict WARN. Reasons: 13 residual suspects post-interpolation; peak |ω₂| 2402°/s &gt; 1500°/s physical rule-of-thumb; 33 arm-length violation(s) (max deviation 27.7%) — tracker latched on wrong object; 13 frame(s) with |Δω| spike (unphysical acceleration)</t>
         </is>
       </c>
     </row>
@@ -1419,20 +1419,20 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>1.49</v>
+        <v>1.45</v>
       </c>
       <c r="I10" t="n">
         <v>1.12</v>
       </c>
       <c r="J10" t="n">
-        <v>1.49</v>
+        <v>1.45</v>
       </c>
       <c r="K10" t="n">
         <v>2681</v>
       </c>
       <c r="L10" s="3" t="inlineStr">
         <is>
-          <t>23 runs (top 5 by duration): f455–f459 (7.6s–7.7s, 0.1s) | f85–f88 (1.4s–1.5s, 0.1s) | f222–f224 (3.7s–3.7s, 0.0s) | f259–f260 (4.3s–4.3s, 0.0s) | f523–f524 (8.7s–8.7s, 0.0s) ... and 18 more</t>
+          <t>21 runs (top 5 by duration): f455–f459 (7.6s–7.7s, 0.1s) | f85–f88 (1.4s–1.5s, 0.1s) | f222–f224 (3.7s–3.7s, 0.0s) | f259–f260 (4.3s–4.3s, 0.0s) | f523–f524 (8.7s–8.7s, 0.0s) ... and 16 more</t>
         </is>
       </c>
       <c r="M10" s="4" t="inlineStr">
@@ -1484,7 +1484,7 @@
         <is>
           <t>Repeat trial of th1_p090_th2_p000. Registered during measurements/ migration.
 ⚠ repeat trial
-verification: manually accepted via chaos next</t>
+verification: DOWNGRADED via chaos audit on 2026-05-02: was 'verified'; new verdict WARN. Reasons: 71 residual suspects post-interpolation; peak |ω₂| 2092°/s &gt; 1500°/s physical rule-of-thumb; 43 arm-length violation(s) (max deviation 30.8%) — tracker latched on wrong object; 71 frame(s) with |Δω| spike (unphysical acceleration)</t>
         </is>
       </c>
     </row>
@@ -1680,55 +1680,55 @@
       </c>
       <c r="V12" s="3" t="inlineStr">
         <is>
-          <t>verification: dropout, suspects, and ω all within thresholds</t>
+          <t>verification: DOWNGRADED via chaos audit on 2026-05-02: was 'verified'; new verdict WARN. Reasons: 7 residual suspects post-interpolation; 7 frame(s) with |Δω| spike (unphysical acceleration)</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>th1_p091_th2_m001</t>
+          <t>th1_p094_th2_p000_r2</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>DSC_0162</t>
+          <t>th1_p094_th2_p000_r2</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>th1_p091_th2_m001.mov</t>
+          <t>th1_p094_th2_p000_2.mov</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E13" t="n">
-        <v>90.354</v>
+        <v>88.93899999999999</v>
       </c>
       <c r="F13" t="n">
-        <v>-1.406</v>
+        <v>72.705</v>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
           <t>TRACKED — analysis pending</t>
         </is>
       </c>
-      <c r="H13" s="2" t="n">
-        <v>5.77</v>
+      <c r="H13" t="n">
+        <v>0</v>
       </c>
       <c r="I13" t="n">
         <v>0</v>
       </c>
       <c r="J13" t="n">
-        <v>5.77</v>
+        <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>1958</v>
+        <v>1353</v>
       </c>
       <c r="L13" s="3" t="inlineStr">
         <is>
-          <t>10 runs: f115 (1.9s, isolated) | f146–f147 (2.4s–2.5s, 0.0s) | f157–f161 (2.6s–2.7s, 0.1s) | f163 (2.7s, isolated) | f165–f166 (2.8s–2.8s, 0.0s) | f196 (3.3s, isolated) | f198–f250 (3.3s–4.2s, 0.9s) | f252–f291 (4.2s–4.9s, 0.7s) | f293–f299 (4.9s–5.0s, 0.1s) | f301 (5.0s, isolated)</t>
+          <t>none</t>
         </is>
       </c>
       <c r="M13" s="4" t="inlineStr">
@@ -1773,39 +1773,40 @@
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>per-video</t>
+          <t>global</t>
         </is>
       </c>
       <c r="V13" s="3" t="inlineStr">
         <is>
-          <t>verification: PASS via WARN-band manual triage 2026-05-01. Smooth coupled oscillation over 33s, 0 hidden suspects, 9.6% dropout entirely in holding phase. Tracked via manual_correction; registry dropout_rate_pct field is stale — see verification.csv for ground truth.</t>
+          <t>Repeat trial of th1_p094_th2_p000. Registered during measurements/ migration.
+⚠ repeat trial</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>th1_p090_th2_p000</t>
+          <t>th1_p093_th2_m002</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>DSC_0160</t>
+          <t>DSC_0156</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>th1_p090_th2_p000.mov</t>
+          <t>th1_p093_th2_m002.mov</t>
         </is>
       </c>
       <c r="D14" t="n">
         <v>1</v>
       </c>
       <c r="E14" t="n">
-        <v>91.06100000000001</v>
+        <v>90</v>
       </c>
       <c r="F14" t="n">
-        <v>1.414</v>
+        <v>-2.148</v>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
@@ -1813,20 +1814,20 @@
         </is>
       </c>
       <c r="H14" t="n">
-        <v>0</v>
+        <v>0.04</v>
       </c>
       <c r="I14" t="n">
         <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>0</v>
+        <v>0.04</v>
       </c>
       <c r="K14" t="n">
-        <v>88</v>
+        <v>2599</v>
       </c>
       <c r="L14" s="3" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>1 isolated frame</t>
         </is>
       </c>
       <c r="M14" s="4" t="inlineStr">
@@ -1871,7 +1872,7 @@
       </c>
       <c r="U14" t="inlineStr">
         <is>
-          <t>global</t>
+          <t>per-video</t>
         </is>
       </c>
       <c r="V14" s="3" t="inlineStr"/>
@@ -1879,66 +1880,58 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>th1_p092_th2_m002</t>
+          <t>th1_p093_th2_m000</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>DSC_0161</t>
+          <t>DSC_0157</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>th1_p092_th2_m002.mov</t>
+          <t>th1_p093_th2_m000.mov</t>
         </is>
       </c>
       <c r="D15" t="n">
         <v>1</v>
       </c>
       <c r="E15" t="n">
-        <v>91.77</v>
+        <v>90</v>
       </c>
       <c r="F15" t="n">
-        <v>-2.13</v>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>-1.768</v>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>TRACKED — analysis pending</t>
+        </is>
+      </c>
+      <c r="H15" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="K15" t="n">
+        <v>2037</v>
       </c>
       <c r="L15" s="3" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M15" s="5" t="inlineStr">
-        <is>
-          <t>❌</t>
-        </is>
-      </c>
-      <c r="N15" s="5" t="inlineStr">
-        <is>
-          <t>❌</t>
+          <t>1 run: f102–f104 (1.7s–1.7s, 0.0s)</t>
+        </is>
+      </c>
+      <c r="M15" s="4" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="N15" s="4" t="inlineStr">
+        <is>
+          <t>✅</t>
         </is>
       </c>
       <c r="O15" s="5" t="inlineStr">
@@ -1981,66 +1974,58 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>th1_p092_th2_p000</t>
+          <t>th1_p091_th2_m001</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>DSC_0159</t>
+          <t>DSC_0162</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>th1_p092_th2_p000.mov</t>
+          <t>th1_p091_th2_m001.mov</t>
         </is>
       </c>
       <c r="D16" t="n">
         <v>1</v>
       </c>
       <c r="E16" t="n">
-        <v>92.11</v>
+        <v>90.354</v>
       </c>
       <c r="F16" t="n">
-        <v>0</v>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>-1.406</v>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>TRACKED — analysis pending</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="n">
+        <v>5.77</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0</v>
+      </c>
+      <c r="J16" t="n">
+        <v>5.77</v>
+      </c>
+      <c r="K16" t="n">
+        <v>1958</v>
       </c>
       <c r="L16" s="3" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M16" s="5" t="inlineStr">
-        <is>
-          <t>❌</t>
-        </is>
-      </c>
-      <c r="N16" s="5" t="inlineStr">
-        <is>
-          <t>❌</t>
+          <t>10 runs: f115 (1.9s, isolated) | f146–f147 (2.4s–2.5s, 0.0s) | f157–f161 (2.6s–2.7s, 0.1s) | f163 (2.7s, isolated) | f165–f166 (2.8s–2.8s, 0.0s) | f196 (3.3s, isolated) | f198–f250 (3.3s–4.2s, 0.9s) | f252–f291 (4.2s–4.9s, 0.7s) | f293–f299 (4.9s–5.0s, 0.1s) | f301 (5.0s, isolated)</t>
+        </is>
+      </c>
+      <c r="M16" s="4" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="N16" s="4" t="inlineStr">
+        <is>
+          <t>✅</t>
         </is>
       </c>
       <c r="O16" s="5" t="inlineStr">
@@ -2075,74 +2060,70 @@
       </c>
       <c r="U16" t="inlineStr">
         <is>
-          <t>global</t>
-        </is>
-      </c>
-      <c r="V16" s="3" t="inlineStr"/>
+          <t>per-video</t>
+        </is>
+      </c>
+      <c r="V16" s="3" t="inlineStr">
+        <is>
+          <t>verification: DOWNGRADED via chaos audit on 2026-05-02: was 'verified'; new verdict WARN. Reasons: free-swing dropout 5.8% in 5–10% band; 62 residual suspects post-interpolation; 62 arm-length violation(s) (max deviation 33.1%) — tracker latched on wrong object; 62 frame(s) with |Δω| spike (unphysical acceleration)</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>th1_p093_th2_m002</t>
+          <t>th1_p092_th2_m002</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>DSC_0156</t>
+          <t>DSC_0161</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>th1_p093_th2_m002.mov</t>
+          <t>th1_p092_th2_m002.mov</t>
         </is>
       </c>
       <c r="D17" t="n">
         <v>1</v>
       </c>
       <c r="E17" t="n">
-        <v>92.83</v>
+        <v>90.703</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.73</v>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>-2.108</v>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>TRACKED — analysis pending</t>
+        </is>
+      </c>
+      <c r="H17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" t="n">
+        <v>2453</v>
       </c>
       <c r="L17" s="3" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M17" s="5" t="inlineStr">
-        <is>
-          <t>❌</t>
-        </is>
-      </c>
-      <c r="N17" s="5" t="inlineStr">
-        <is>
-          <t>❌</t>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="M17" s="4" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="N17" s="4" t="inlineStr">
+        <is>
+          <t>✅</t>
         </is>
       </c>
       <c r="O17" s="5" t="inlineStr">
@@ -2177,7 +2158,7 @@
       </c>
       <c r="U17" t="inlineStr">
         <is>
-          <t>global</t>
+          <t>per-video</t>
         </is>
       </c>
       <c r="V17" s="3" t="inlineStr"/>
@@ -2185,66 +2166,58 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>th1_p093_th2_m000</t>
+          <t>th1_p090_th2_p000</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>DSC_0157</t>
+          <t>DSC_0160</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>th1_p093_th2_m000.mov</t>
+          <t>th1_p090_th2_p000.mov</t>
         </is>
       </c>
       <c r="D18" t="n">
         <v>1</v>
       </c>
       <c r="E18" t="n">
-        <v>92.84</v>
+        <v>91.06100000000001</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.35</v>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>1.414</v>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>TRACKED — analysis pending</t>
+        </is>
+      </c>
+      <c r="H18" t="n">
+        <v>0</v>
+      </c>
+      <c r="I18" t="n">
+        <v>0</v>
+      </c>
+      <c r="J18" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" t="n">
+        <v>88</v>
       </c>
       <c r="L18" s="3" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M18" s="5" t="inlineStr">
-        <is>
-          <t>❌</t>
-        </is>
-      </c>
-      <c r="N18" s="5" t="inlineStr">
-        <is>
-          <t>❌</t>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="M18" s="4" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="N18" s="4" t="inlineStr">
+        <is>
+          <t>✅</t>
         </is>
       </c>
       <c r="O18" s="5" t="inlineStr">
@@ -2287,66 +2260,58 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>th1_p094_th2_p000</t>
+          <t>th1_p092_th2_p000</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>DSC_0158</t>
+          <t>DSC_0159</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>th1_p094_th2_p000.mov</t>
+          <t>th1_p092_th2_p000.mov</t>
         </is>
       </c>
       <c r="D19" t="n">
         <v>1</v>
       </c>
       <c r="E19" t="n">
-        <v>93.58</v>
+        <v>92.121</v>
       </c>
       <c r="F19" t="n">
-        <v>0.35</v>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>TRACKED — analysis pending</t>
+        </is>
+      </c>
+      <c r="H19" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0</v>
+      </c>
+      <c r="J19" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="K19" t="n">
+        <v>2496</v>
       </c>
       <c r="L19" s="3" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M19" s="5" t="inlineStr">
-        <is>
-          <t>❌</t>
-        </is>
-      </c>
-      <c r="N19" s="5" t="inlineStr">
-        <is>
-          <t>❌</t>
+          <t>3 runs: f84 (1.4s, isolated) | f167–f168 (2.8s–2.8s, 0.0s) | f210–f211 (3.5s–3.5s, 0.0s)</t>
+        </is>
+      </c>
+      <c r="M19" s="4" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="N19" s="4" t="inlineStr">
+        <is>
+          <t>✅</t>
         </is>
       </c>
       <c r="O19" s="5" t="inlineStr">
@@ -2381,7 +2346,7 @@
       </c>
       <c r="U19" t="inlineStr">
         <is>
-          <t>global</t>
+          <t>per-video</t>
         </is>
       </c>
       <c r="V19" s="3" t="inlineStr"/>
@@ -2389,66 +2354,58 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>th1_p094_th2_p000_r2</t>
+          <t>th1_p094_th2_p000</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>th1_p094_th2_p000_r2</t>
+          <t>DSC_0158</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>th1_p094_th2_p000_2.mov</t>
+          <t>th1_p094_th2_p000.mov</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E20" t="n">
-        <v>93.58</v>
+        <v>92.827</v>
       </c>
       <c r="F20" t="n">
-        <v>0.35</v>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>-0.349</v>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>TRACKED — analysis pending</t>
+        </is>
+      </c>
+      <c r="H20" t="n">
+        <v>0</v>
+      </c>
+      <c r="I20" t="n">
+        <v>0</v>
+      </c>
+      <c r="J20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K20" t="n">
+        <v>2351</v>
       </c>
       <c r="L20" s="3" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M20" s="5" t="inlineStr">
-        <is>
-          <t>❌</t>
-        </is>
-      </c>
-      <c r="N20" s="5" t="inlineStr">
-        <is>
-          <t>❌</t>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="M20" s="4" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="N20" s="4" t="inlineStr">
+        <is>
+          <t>✅</t>
         </is>
       </c>
       <c r="O20" s="5" t="inlineStr">
@@ -2483,15 +2440,10 @@
       </c>
       <c r="U20" t="inlineStr">
         <is>
-          <t>global</t>
-        </is>
-      </c>
-      <c r="V20" s="3" t="inlineStr">
-        <is>
-          <t>Repeat trial of th1_p094_th2_p000. Registered during measurements/ migration.
-⚠ repeat trial</t>
-        </is>
-      </c>
+          <t>per-video</t>
+        </is>
+      </c>
+      <c r="V20" s="3" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2513,49 +2465,41 @@
         <v>1</v>
       </c>
       <c r="E21" t="n">
-        <v>115.6</v>
+        <v>115.145</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.41</v>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>-2.459</v>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>TRACKED — analysis pending</t>
+        </is>
+      </c>
+      <c r="H21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K21" t="n">
+        <v>1966</v>
       </c>
       <c r="L21" s="3" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M21" s="5" t="inlineStr">
-        <is>
-          <t>❌</t>
-        </is>
-      </c>
-      <c r="N21" s="5" t="inlineStr">
-        <is>
-          <t>❌</t>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="M21" s="4" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="N21" s="4" t="inlineStr">
+        <is>
+          <t>✅</t>
         </is>
       </c>
       <c r="O21" s="5" t="inlineStr">
@@ -2590,7 +2534,7 @@
       </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>global</t>
+          <t>per-video</t>
         </is>
       </c>
       <c r="V21" s="3" t="inlineStr"/>
@@ -2615,49 +2559,41 @@
         <v>1</v>
       </c>
       <c r="E22" t="n">
-        <v>138.25</v>
+        <v>136.992</v>
       </c>
       <c r="F22" t="n">
-        <v>-2.12</v>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>-3.16</v>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>TRACKED — analysis pending</t>
+        </is>
+      </c>
+      <c r="H22" t="n">
+        <v>0</v>
+      </c>
+      <c r="I22" t="n">
+        <v>0</v>
+      </c>
+      <c r="J22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K22" t="n">
+        <v>2587</v>
       </c>
       <c r="L22" s="3" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M22" s="5" t="inlineStr">
-        <is>
-          <t>❌</t>
-        </is>
-      </c>
-      <c r="N22" s="5" t="inlineStr">
-        <is>
-          <t>❌</t>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="M22" s="4" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="N22" s="4" t="inlineStr">
+        <is>
+          <t>✅</t>
         </is>
       </c>
       <c r="O22" s="5" t="inlineStr">
@@ -2692,7 +2628,7 @@
       </c>
       <c r="U22" t="inlineStr">
         <is>
-          <t>global</t>
+          <t>per-video</t>
         </is>
       </c>
       <c r="V22" s="3" t="inlineStr"/>
@@ -2717,49 +2653,41 @@
         <v>1</v>
       </c>
       <c r="E23" t="n">
-        <v>140.33</v>
+        <v>140.511</v>
       </c>
       <c r="F23" t="n">
-        <v>89.29000000000001</v>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>87.709</v>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>TRACKED — analysis pending</t>
+        </is>
+      </c>
+      <c r="H23" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="I23" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="J23" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="K23" t="n">
+        <v>1094</v>
       </c>
       <c r="L23" s="3" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M23" s="5" t="inlineStr">
-        <is>
-          <t>❌</t>
-        </is>
-      </c>
-      <c r="N23" s="5" t="inlineStr">
-        <is>
-          <t>❌</t>
+          <t>4 runs: f90–f103 (1.5s–1.7s, 0.2s) | f532 (8.9s, isolated) | f637 (10.6s, isolated) | f676–f677 (11.3s–11.3s, 0.0s)</t>
+        </is>
+      </c>
+      <c r="M23" s="4" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="N23" s="4" t="inlineStr">
+        <is>
+          <t>✅</t>
         </is>
       </c>
       <c r="O23" s="5" t="inlineStr">
@@ -2794,7 +2722,7 @@
       </c>
       <c r="U23" t="inlineStr">
         <is>
-          <t>global</t>
+          <t>per-video</t>
         </is>
       </c>
       <c r="V23" s="3" t="inlineStr"/>
@@ -3269,7 +3197,7 @@
       </c>
       <c r="V28" s="3" t="inlineStr">
         <is>
-          <t>verification: verify_tracking.py @ 2500 deg/s cap: 70 dropouts (4.98%, mostly early high-energy frames), 2 suspect frames interpolated, 0 suspects after re-verification.</t>
+          <t>verification: DOWNGRADED via chaos audit on 2026-05-02: was 'verified'; new verdict WARN. Reasons: free-swing dropout 5.0% in 5–10% band; 116 residual suspects post-interpolation; peak |ω₂| 1824°/s &gt; 1500°/s physical rule-of-thumb; 19 arm-length violation(s) (max deviation 40.9%) — tracker latched on wrong object; 116 frame(s) with |Δω| spike (unphysical acceleration)</t>
         </is>
       </c>
     </row>
@@ -3542,7 +3470,7 @@
       </c>
       <c r="V2" s="3" t="inlineStr">
         <is>
-          <t>verification: PASS via WARN-band manual triage 2026-05-01. 12 residual suspects post-interpolation are paired-frame artefacts in the first 15s of chaos (0.04% of 30k frames); 0% dropout overall, smooth damping for the remaining ~500s.</t>
+          <t>verification: DOWNGRADED via chaos audit on 2026-05-02: was 'verified'; new verdict WARN. Reasons: 251 residual suspects post-interpolation; peak |ω₂| 3466°/s &gt; 1500°/s physical rule-of-thumb; 13 holding-phase suspects (|ω| &gt; 100°/s while stationary); 103 arm-length violation(s) (max deviation 32.2%) — tracker latched on wrong object; 243 frame(s) with |Δω| spike (unphysical acceleration)</t>
         </is>
       </c>
       <c r="W2" t="n">
@@ -3552,7 +3480,7 @@
         <v>30897</v>
       </c>
       <c r="Y2" t="n">
-        <v>12</v>
+        <v>221</v>
       </c>
       <c r="Z2" t="n">
         <v>13.1371</v>

--- a/data/status_report.xlsx
+++ b/data/status_report.xlsx
@@ -918,10 +918,10 @@
         <v>1</v>
       </c>
       <c r="E5" t="n">
-        <v>35.538</v>
+        <v>31.178</v>
       </c>
       <c r="F5" t="n">
-        <v>90.58199999999999</v>
+        <v>98.04300000000001</v>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
@@ -929,20 +929,20 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>1.23</v>
+        <v>0.38</v>
       </c>
       <c r="I5" t="n">
-        <v>0.47</v>
+        <v>0.28</v>
       </c>
       <c r="J5" t="n">
-        <v>1.23</v>
+        <v>0.38</v>
       </c>
       <c r="K5" t="n">
         <v>1059</v>
       </c>
       <c r="L5" s="3" t="inlineStr">
         <is>
-          <t>2 runs: f97–f98 (1.6s–1.6s, 0.0s) | f171–f181 (2.9s–3.0s, 0.2s)</t>
+          <t>1 run: f174–f177 (2.9s–3.0s, 0.1s)</t>
         </is>
       </c>
       <c r="M5" s="4" t="inlineStr">
@@ -1016,10 +1016,10 @@
         <v>1</v>
       </c>
       <c r="E6" t="n">
-        <v>42.25</v>
+        <v>37.376</v>
       </c>
       <c r="F6" t="n">
-        <v>1.725</v>
+        <v>1.406</v>
       </c>
       <c r="G6" s="7" t="inlineStr">
         <is>
@@ -1090,7 +1090,7 @@
       </c>
       <c r="V6" s="3" t="inlineStr">
         <is>
-          <t>verification: verify_tracking.py @ 2500 deg/s cap: 0 dropouts, 0 suspects across 1239 frames (164 holding, 1075 free_swing). All physics plausible.</t>
+          <t>verification: dropout, suspects, and ω all within thresholds</t>
         </is>
       </c>
     </row>
@@ -1188,7 +1188,7 @@
       </c>
       <c r="V7" s="3" t="inlineStr">
         <is>
-          <t>verification: PASS via manual_correction strict-physics flow.</t>
+          <t>verification: DOWNGRADED via chaos audit on 2026-05-02: was 'verified'; new verdict WARN. Reasons: 3 frame(s) show rolling energy spike (&gt;2.0× baseline) — tracker likely jumped briefly to wrong object</t>
         </is>
       </c>
     </row>
@@ -1212,10 +1212,10 @@
         <v>1</v>
       </c>
       <c r="E8" t="n">
-        <v>55.037</v>
+        <v>48.662</v>
       </c>
       <c r="F8" t="n">
-        <v>-2.108</v>
+        <v>-1.746</v>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
@@ -1286,7 +1286,7 @@
       </c>
       <c r="V8" s="3" t="inlineStr">
         <is>
-          <t>verification: DOWNGRADED via chaos audit on 2026-05-02: was 'verified'; new verdict WARN. Reasons: 1 residual suspects post-interpolation; 1 frame(s) with |Δω| spike (unphysical acceleration)</t>
+          <t>verification: dropout, suspects, and ω all within thresholds</t>
         </is>
       </c>
     </row>
@@ -1310,7 +1310,7 @@
         <v>1</v>
       </c>
       <c r="E9" t="n">
-        <v>68.199</v>
+        <v>60.624</v>
       </c>
       <c r="F9" t="n">
         <v>90.60299999999999</v>
@@ -1491,48 +1491,48 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>th1_p079_th2_p000</t>
+          <t>th1_p082_th2_p001</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>DSC_0141</t>
+          <t>th1_p082_th2_p001</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>th1_p079_th2_p000.mov</t>
+          <t>th1_p082_th2_p001.mov</t>
         </is>
       </c>
       <c r="D11" t="n">
         <v>1</v>
       </c>
       <c r="E11" t="n">
-        <v>78.27500000000001</v>
+        <v>73.399</v>
       </c>
       <c r="F11" t="n">
-        <v>88.127</v>
+        <v>-0.345</v>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
           <t>TRACKED — analysis pending</t>
         </is>
       </c>
-      <c r="H11" s="2" t="n">
-        <v>5.62</v>
+      <c r="H11" t="n">
+        <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>0.5600000000000001</v>
+        <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>5.06</v>
+        <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>178</v>
+        <v>1573</v>
       </c>
       <c r="L11" s="3" t="inlineStr">
         <is>
-          <t>1 run: f250–f259 (4.2s–4.3s, 0.2s)</t>
+          <t>none</t>
         </is>
       </c>
       <c r="M11" s="4" t="inlineStr">
@@ -1577,60 +1577,60 @@
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>global</t>
+          <t>per-video</t>
         </is>
       </c>
       <c r="V11" s="3" t="inlineStr">
         <is>
-          <t>⚠ no per-video HSV calibration</t>
+          <t>verification: dropout, suspects, and ω all within thresholds</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>th1_p082_th2_p001</t>
+          <t>th1_p079_th2_p000</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>th1_p082_th2_p001</t>
+          <t>DSC_0141</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>th1_p082_th2_p001.mov</t>
+          <t>th1_p079_th2_p000.mov</t>
         </is>
       </c>
       <c r="D12" t="n">
         <v>1</v>
       </c>
       <c r="E12" t="n">
-        <v>81.81999999999999</v>
+        <v>78.27500000000001</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.345</v>
+        <v>88.127</v>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
           <t>TRACKED — analysis pending</t>
         </is>
       </c>
-      <c r="H12" t="n">
-        <v>0</v>
+      <c r="H12" s="2" t="n">
+        <v>5.62</v>
       </c>
       <c r="I12" t="n">
-        <v>0</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="J12" t="n">
-        <v>0</v>
+        <v>5.06</v>
       </c>
       <c r="K12" t="n">
-        <v>1573</v>
+        <v>178</v>
       </c>
       <c r="L12" s="3" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>1 run: f250–f259 (4.2s–4.3s, 0.2s)</t>
         </is>
       </c>
       <c r="M12" s="4" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>per-video</t>
+          <t>global</t>
         </is>
       </c>
       <c r="V12" s="3" t="inlineStr">
         <is>
-          <t>verification: DOWNGRADED via chaos audit on 2026-05-02: was 'verified'; new verdict WARN. Reasons: 7 residual suspects post-interpolation; 7 frame(s) with |Δω| spike (unphysical acceleration)</t>
+          <t>⚠ no per-video HSV calibration</t>
         </is>
       </c>
     </row>
@@ -1704,10 +1704,10 @@
         <v>2</v>
       </c>
       <c r="E13" t="n">
-        <v>88.93899999999999</v>
+        <v>80.82599999999999</v>
       </c>
       <c r="F13" t="n">
-        <v>72.705</v>
+        <v>-86.78100000000001</v>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>

--- a/data/status_report.xlsx
+++ b/data/status_report.xlsx
@@ -1408,7 +1408,7 @@
         <v>2</v>
       </c>
       <c r="E10" t="n">
-        <v>71.67700000000001</v>
+        <v>63.88</v>
       </c>
       <c r="F10" t="n">
         <v>-82.26600000000001</v>
@@ -1419,20 +1419,20 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>1.45</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="I10" t="n">
-        <v>1.12</v>
+        <v>0.52</v>
       </c>
       <c r="J10" t="n">
-        <v>1.45</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="K10" t="n">
         <v>2681</v>
       </c>
       <c r="L10" s="3" t="inlineStr">
         <is>
-          <t>21 runs (top 5 by duration): f455–f459 (7.6s–7.7s, 0.1s) | f85–f88 (1.4s–1.5s, 0.1s) | f222–f224 (3.7s–3.7s, 0.0s) | f259–f260 (4.3s–4.3s, 0.0s) | f523–f524 (8.7s–8.7s, 0.0s) ... and 16 more</t>
+          <t>7 runs: f85–f88 (1.4s–1.5s, 0.1s) | f163 (2.7s, isolated) | f223–f224 (3.7s–3.7s, 0.0s) | f259–f260 (4.3s–4.3s, 0.0s) | f419–f420 (7.0s–7.0s, 0.0s) | f561–f562 (9.4s–9.4s, 0.0s) | f666–f667 (11.1s–11.1s, 0.0s)</t>
         </is>
       </c>
       <c r="M10" s="4" t="inlineStr">
@@ -1715,10 +1715,10 @@
         </is>
       </c>
       <c r="H13" t="n">
-        <v>0</v>
+        <v>0.15</v>
       </c>
       <c r="I13" t="n">
-        <v>0</v>
+        <v>0.15</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -1728,7 +1728,7 @@
       </c>
       <c r="L13" s="3" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>1 run: f97–f98 (1.6s–1.6s, 0.0s)</t>
         </is>
       </c>
       <c r="M13" s="4" t="inlineStr">
@@ -1786,27 +1786,27 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>th1_p093_th2_m002</t>
+          <t>th1_p092_th2_m002</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>DSC_0156</t>
+          <t>DSC_0161</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>th1_p093_th2_m002.mov</t>
+          <t>th1_p092_th2_m002.mov</t>
         </is>
       </c>
       <c r="D14" t="n">
         <v>1</v>
       </c>
       <c r="E14" t="n">
-        <v>90</v>
+        <v>81.968</v>
       </c>
       <c r="F14" t="n">
-        <v>-2.148</v>
+        <v>-1.757</v>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
@@ -1814,20 +1814,20 @@
         </is>
       </c>
       <c r="H14" t="n">
-        <v>0.04</v>
+        <v>0</v>
       </c>
       <c r="I14" t="n">
         <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>0.04</v>
+        <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>2599</v>
+        <v>2453</v>
       </c>
       <c r="L14" s="3" t="inlineStr">
         <is>
-          <t>1 isolated frame</t>
+          <t>none</t>
         </is>
       </c>
       <c r="M14" s="4" t="inlineStr">
@@ -1880,27 +1880,27 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>th1_p093_th2_m000</t>
+          <t>th1_p090_th2_p000</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>DSC_0157</t>
+          <t>DSC_0160</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>th1_p093_th2_m000.mov</t>
+          <t>th1_p090_th2_p000.mov</t>
         </is>
       </c>
       <c r="D15" t="n">
         <v>1</v>
       </c>
       <c r="E15" t="n">
-        <v>90</v>
+        <v>82.26600000000001</v>
       </c>
       <c r="F15" t="n">
-        <v>-1.768</v>
+        <v>1.768</v>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
@@ -1908,20 +1908,20 @@
         </is>
       </c>
       <c r="H15" t="n">
-        <v>0.15</v>
+        <v>0</v>
       </c>
       <c r="I15" t="n">
-        <v>0.15</v>
+        <v>0</v>
       </c>
       <c r="J15" t="n">
-        <v>0.15</v>
+        <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>2037</v>
+        <v>88</v>
       </c>
       <c r="L15" s="3" t="inlineStr">
         <is>
-          <t>1 run: f102–f104 (1.7s–1.7s, 0.0s)</t>
+          <t>none</t>
         </is>
       </c>
       <c r="M15" s="4" t="inlineStr">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="U15" t="inlineStr">
         <is>
-          <t>per-video</t>
+          <t>global</t>
         </is>
       </c>
       <c r="V15" s="3" t="inlineStr"/>
@@ -1974,48 +1974,48 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>th1_p091_th2_m001</t>
+          <t>th1_p093_th2_m002</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>DSC_0162</t>
+          <t>DSC_0156</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>th1_p091_th2_m001.mov</t>
+          <t>th1_p093_th2_m002.mov</t>
         </is>
       </c>
       <c r="D16" t="n">
         <v>1</v>
       </c>
       <c r="E16" t="n">
-        <v>90.354</v>
+        <v>90</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.406</v>
+        <v>-2.148</v>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
           <t>TRACKED — analysis pending</t>
         </is>
       </c>
-      <c r="H16" s="2" t="n">
-        <v>5.77</v>
+      <c r="H16" t="n">
+        <v>0.04</v>
       </c>
       <c r="I16" t="n">
         <v>0</v>
       </c>
       <c r="J16" t="n">
-        <v>5.77</v>
+        <v>0.04</v>
       </c>
       <c r="K16" t="n">
-        <v>1958</v>
+        <v>2599</v>
       </c>
       <c r="L16" s="3" t="inlineStr">
         <is>
-          <t>10 runs: f115 (1.9s, isolated) | f146–f147 (2.4s–2.5s, 0.0s) | f157–f161 (2.6s–2.7s, 0.1s) | f163 (2.7s, isolated) | f165–f166 (2.8s–2.8s, 0.0s) | f196 (3.3s, isolated) | f198–f250 (3.3s–4.2s, 0.9s) | f252–f291 (4.2s–4.9s, 0.7s) | f293–f299 (4.9s–5.0s, 0.1s) | f301 (5.0s, isolated)</t>
+          <t>1 isolated frame</t>
         </is>
       </c>
       <c r="M16" s="4" t="inlineStr">
@@ -2063,36 +2063,32 @@
           <t>per-video</t>
         </is>
       </c>
-      <c r="V16" s="3" t="inlineStr">
-        <is>
-          <t>verification: DOWNGRADED via chaos audit on 2026-05-02: was 'verified'; new verdict WARN. Reasons: free-swing dropout 5.8% in 5–10% band; 62 residual suspects post-interpolation; 62 arm-length violation(s) (max deviation 33.1%) — tracker latched on wrong object; 62 frame(s) with |Δω| spike (unphysical acceleration)</t>
-        </is>
-      </c>
+      <c r="V16" s="3" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>th1_p092_th2_m002</t>
+          <t>th1_p093_th2_m000</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>DSC_0161</t>
+          <t>DSC_0157</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>th1_p092_th2_m002.mov</t>
+          <t>th1_p093_th2_m000.mov</t>
         </is>
       </c>
       <c r="D17" t="n">
         <v>1</v>
       </c>
       <c r="E17" t="n">
-        <v>90.703</v>
+        <v>90</v>
       </c>
       <c r="F17" t="n">
-        <v>-2.108</v>
+        <v>-1.768</v>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
@@ -2100,20 +2096,20 @@
         </is>
       </c>
       <c r="H17" t="n">
-        <v>0</v>
+        <v>0.15</v>
       </c>
       <c r="I17" t="n">
-        <v>0</v>
+        <v>0.15</v>
       </c>
       <c r="J17" t="n">
-        <v>0</v>
+        <v>0.15</v>
       </c>
       <c r="K17" t="n">
-        <v>2453</v>
+        <v>2037</v>
       </c>
       <c r="L17" s="3" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>1 run: f102–f104 (1.7s–1.7s, 0.0s)</t>
         </is>
       </c>
       <c r="M17" s="4" t="inlineStr">
@@ -2166,48 +2162,48 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>th1_p090_th2_p000</t>
+          <t>th1_p091_th2_m001</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>DSC_0160</t>
+          <t>DSC_0162</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>th1_p090_th2_p000.mov</t>
+          <t>th1_p091_th2_m001.mov</t>
         </is>
       </c>
       <c r="D18" t="n">
         <v>1</v>
       </c>
       <c r="E18" t="n">
-        <v>91.06100000000001</v>
+        <v>90.354</v>
       </c>
       <c r="F18" t="n">
-        <v>1.414</v>
+        <v>-1.406</v>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
           <t>TRACKED — analysis pending</t>
         </is>
       </c>
-      <c r="H18" t="n">
-        <v>0</v>
+      <c r="H18" s="2" t="n">
+        <v>5.77</v>
       </c>
       <c r="I18" t="n">
         <v>0</v>
       </c>
       <c r="J18" t="n">
-        <v>0</v>
+        <v>5.77</v>
       </c>
       <c r="K18" t="n">
-        <v>88</v>
+        <v>1958</v>
       </c>
       <c r="L18" s="3" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>10 runs: f115 (1.9s, isolated) | f146–f147 (2.4s–2.5s, 0.0s) | f157–f161 (2.6s–2.7s, 0.1s) | f163 (2.7s, isolated) | f165–f166 (2.8s–2.8s, 0.0s) | f196 (3.3s, isolated) | f198–f250 (3.3s–4.2s, 0.9s) | f252–f291 (4.2s–4.9s, 0.7s) | f293–f299 (4.9s–5.0s, 0.1s) | f301 (5.0s, isolated)</t>
         </is>
       </c>
       <c r="M18" s="4" t="inlineStr">
@@ -2252,10 +2248,14 @@
       </c>
       <c r="U18" t="inlineStr">
         <is>
-          <t>global</t>
-        </is>
-      </c>
-      <c r="V18" s="3" t="inlineStr"/>
+          <t>per-video</t>
+        </is>
+      </c>
+      <c r="V18" s="3" t="inlineStr">
+        <is>
+          <t>verification: DOWNGRADED via chaos audit on 2026-05-02: was 'verified'; new verdict WARN. Reasons: free-swing dropout 5.8% in 5–10% band; 62 residual suspects post-interpolation; 62 arm-length violation(s) (max deviation 33.1%) — tracker latched on wrong object; 62 frame(s) with |Δω| spike (unphysical acceleration)</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
